--- a/filtered_true_vs_predicted_with_id.xlsx
+++ b/filtered_true_vs_predicted_with_id.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C313"/>
+  <dimension ref="A1:C220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,23 +452,23 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0387449599802494</v>
+        <v>0.01112724561244249</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>150</v>
+        <v>61</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01288249529898167</v>
+        <v>1214.182861328125</v>
       </c>
     </row>
     <row r="4">
@@ -478,4027 +478,2818 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>200</v>
+        <v>35</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02239006757736206</v>
+        <v>1283.100219726562</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1081</t>
+          <t>1095</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>205</v>
+        <v>166</v>
       </c>
       <c r="C5" t="n">
-        <v>0.006469916552305222</v>
+        <v>1456.375610351562</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1109</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>34.267</v>
+        <v>270.4</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02687149867415428</v>
+        <v>1785.0859375</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>451.53</v>
+        <v>1059.62</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02489081956446171</v>
+        <v>1765.819580078125</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>320.95</v>
+        <v>335.03</v>
       </c>
       <c r="C8" t="n">
-        <v>32.33563995361328</v>
+        <v>0.01357313431799412</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1109</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>848.42</v>
+        <v>13.34</v>
       </c>
       <c r="C9" t="n">
-        <v>0.004001860972493887</v>
+        <v>1753.915283203125</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1109</t>
+          <t>1163</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>165</v>
+        <v>23</v>
       </c>
       <c r="C10" t="n">
-        <v>14.06515979766846</v>
+        <v>0.01537336129695177</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>117</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>100</v>
+        <v>159.78</v>
       </c>
       <c r="C11" t="n">
-        <v>0.009799523279070854</v>
+        <v>0.02377860620617867</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1756.82</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0115722892805934</v>
+        <v>0.01297876518219709</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>814.85</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>17.78246688842773</v>
+        <v>0.007279780693352222</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>275</v>
+        <v>106</v>
       </c>
       <c r="C14" t="n">
-        <v>0.01001401711255312</v>
+        <v>0.006340757012367249</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>122</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>198</v>
+        <v>25.6</v>
       </c>
       <c r="C15" t="n">
-        <v>0.03538965806365013</v>
+        <v>0.01283220481127501</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>1225</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>150</v>
+        <v>173.49</v>
       </c>
       <c r="C16" t="n">
-        <v>0.002989029046148062</v>
+        <v>0.006235533393919468</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1158</t>
+          <t>123</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="C17" t="n">
-        <v>0.06042587012052536</v>
+        <v>0.01124641578644514</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>75</v>
+        <v>300</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01035682111978531</v>
+        <v>0.01304991822689772</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>132</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>23.38</v>
+        <v>34.5</v>
       </c>
       <c r="C19" t="n">
-        <v>0.01001301687210798</v>
+        <v>0.009626070968806744</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>137</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>200</v>
+        <v>113</v>
       </c>
       <c r="C20" t="n">
-        <v>0.02271260693669319</v>
+        <v>112.5519409179688</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>138</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10</v>
+        <v>438.1</v>
       </c>
       <c r="C21" t="n">
-        <v>0.00981893390417099</v>
+        <v>245.14501953125</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1206</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="C22" t="n">
-        <v>0.06483248621225357</v>
+        <v>0.01331471092998981</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>141</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>158</v>
+        <v>6.5</v>
       </c>
       <c r="C23" t="n">
-        <v>0.02695811912417412</v>
+        <v>248.0916748046875</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>142</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>60</v>
+        <v>151.5</v>
       </c>
       <c r="C24" t="n">
-        <v>0.07014233618974686</v>
+        <v>192.0350036621094</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>143</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>26.56</v>
+        <v>953</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0143534392118454</v>
+        <v>311.699951171875</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1219</t>
+          <t>153</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>0.01486928202211857</v>
+        <v>170.6828002929688</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1219</t>
+          <t>158</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="C27" t="n">
-        <v>0.01199890486896038</v>
+        <v>226.2901306152344</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>169</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>92.5</v>
+        <v>94</v>
       </c>
       <c r="C28" t="n">
-        <v>0.01167822629213333</v>
+        <v>0.01731166988611221</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>170</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>98</v>
+        <v>291.4</v>
       </c>
       <c r="C29" t="n">
-        <v>0.007999795489013195</v>
+        <v>0.010331766679883</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1223</t>
+          <t>172</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>25</v>
+        <v>1158.89</v>
       </c>
       <c r="C30" t="n">
-        <v>0.01878008805215359</v>
+        <v>0.02185212820768356</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1225</t>
+          <t>173</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>350</v>
+        <v>9251.719999999999</v>
       </c>
       <c r="C31" t="n">
-        <v>0.01345261465758085</v>
+        <v>0.06485572457313538</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1225</t>
+          <t>176</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>20</v>
+        <v>160</v>
       </c>
       <c r="C32" t="n">
-        <v>0.03068284317851067</v>
+        <v>0.00748767564073205</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>177</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>20</v>
       </c>
       <c r="C33" t="n">
-        <v>0.01540089584887028</v>
+        <v>0.008458978496491909</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1235</t>
+          <t>179</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="C34" t="n">
-        <v>0.01007805019617081</v>
+        <v>0.007611302193254232</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>181</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>34.5</v>
+        <v>100</v>
       </c>
       <c r="C35" t="n">
-        <v>0.008174140006303787</v>
+        <v>0.0229012742638588</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>182</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>145</v>
+        <v>129.4</v>
       </c>
       <c r="C36" t="n">
-        <v>0.008187318220734596</v>
+        <v>0.02765802480280399</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>187</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>20</v>
       </c>
       <c r="C37" t="n">
-        <v>0.005719513632357121</v>
+        <v>0.01178150903433561</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>189</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="C38" t="n">
-        <v>0.002364815445616841</v>
+        <v>0.01036293990910053</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>193</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>104.26</v>
+        <v>21.27</v>
       </c>
       <c r="C39" t="n">
-        <v>0.003513207659125328</v>
+        <v>0.01007942669093609</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>194</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2105149328708649</v>
+        <v>0.00980749074369669</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>196</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>220</v>
+        <v>44.14</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0009961768519133329</v>
+        <v>0.009580088779330254</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>197</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="C42" t="n">
-        <v>0.01083472650498152</v>
+        <v>0.02339113876223564</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2142.12</v>
+        <v>23</v>
       </c>
       <c r="C43" t="n">
-        <v>0.01244094595313072</v>
+        <v>0.01195498369634151</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>203</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>500</v>
+        <v>1030.63</v>
       </c>
       <c r="C44" t="n">
-        <v>0.013717882335186</v>
+        <v>0.02758749946951866</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>204</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>145</v>
+        <v>1461.96</v>
       </c>
       <c r="C45" t="n">
-        <v>0.01661697775125504</v>
+        <v>0.02062669768929482</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>207</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="C46" t="n">
-        <v>0.016964141279459</v>
+        <v>0.2155287265777588</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>208</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>200</v>
+        <v>146</v>
       </c>
       <c r="C47" t="n">
-        <v>0.01357712410390377</v>
+        <v>0.01753089018166065</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>700</v>
+        <v>130</v>
       </c>
       <c r="C48" t="n">
-        <v>0.01385952532291412</v>
+        <v>0.0111288595944643</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>213</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>40</v>
+        <v>687.1</v>
       </c>
       <c r="C49" t="n">
-        <v>0.007994277402758598</v>
+        <v>0.01902708038687706</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>214</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>10</v>
+        <v>953</v>
       </c>
       <c r="C50" t="n">
-        <v>0.02454881370067596</v>
+        <v>0.0207593347877264</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>20</v>
+        <v>140</v>
       </c>
       <c r="C51" t="n">
-        <v>0.02065461501479149</v>
+        <v>0.01312807016074657</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>225</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>10</v>
+        <v>383.45</v>
       </c>
       <c r="C52" t="n">
-        <v>0.008171136491000652</v>
+        <v>0.02569554373621941</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>242</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="C53" t="n">
-        <v>0.008174298331141472</v>
+        <v>0.03005289472639561</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>247</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="C54" t="n">
-        <v>0.02524474263191223</v>
+        <v>0.03195869922637939</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>248</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>23.97</v>
+        <v>120</v>
       </c>
       <c r="C55" t="n">
-        <v>0.009994545951485634</v>
+        <v>0.0411824956536293</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>256</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>232.125</v>
+        <v>25</v>
       </c>
       <c r="C56" t="n">
-        <v>0.02352027408778667</v>
+        <v>0.02081135846674442</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>122.76</v>
+        <v>200</v>
       </c>
       <c r="C57" t="n">
-        <v>0.009976310655474663</v>
+        <v>0.01591860130429268</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>261</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>256.78</v>
+        <v>26</v>
       </c>
       <c r="C58" t="n">
-        <v>0.02041151747107506</v>
+        <v>0.01819173991680145</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>276</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>270.16</v>
+        <v>20</v>
       </c>
       <c r="C59" t="n">
-        <v>0.009791595861315727</v>
+        <v>0.01484734378755093</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>277</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>537</v>
+        <v>92</v>
       </c>
       <c r="C60" t="n">
-        <v>0.02080646529793739</v>
+        <v>0.02367893047630787</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>278</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>162.25</v>
+        <v>85.87</v>
       </c>
       <c r="C61" t="n">
-        <v>0.03982657939195633</v>
+        <v>0.008957989513874054</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>279</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>8752.24</v>
+        <v>114.5</v>
       </c>
       <c r="C62" t="n">
-        <v>0.02762496098875999</v>
+        <v>0.005981702357530594</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>281</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>3584.736</v>
+        <v>218</v>
       </c>
       <c r="C63" t="n">
-        <v>0.03307123482227325</v>
+        <v>0.008361038751900196</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>282</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>20</v>
+        <v>258</v>
       </c>
       <c r="C64" t="n">
-        <v>0.03660527616739273</v>
+        <v>0.0196111649274826</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>283</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="C65" t="n">
-        <v>0.03117897734045982</v>
+        <v>0.007874093018472195</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>286</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C66" t="n">
-        <v>0.01141955237835646</v>
+        <v>0.009630708955228329</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>290</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>303.36</v>
+        <v>20</v>
       </c>
       <c r="C67" t="n">
-        <v>0.02699203789234161</v>
+        <v>0.01330242864787579</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>292</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>100</v>
+        <v>627</v>
       </c>
       <c r="C68" t="n">
-        <v>0.02776087261736393</v>
+        <v>0.0149662746116519</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>293</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>105.58</v>
+        <v>472.07</v>
       </c>
       <c r="C69" t="n">
-        <v>0.01748087629675865</v>
+        <v>0.02281797304749489</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>294</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>916.9200000000001</v>
+        <v>85</v>
       </c>
       <c r="C70" t="n">
-        <v>0.009989381767809391</v>
+        <v>0.009905318729579449</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>295</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>250</v>
+        <v>80</v>
       </c>
       <c r="C71" t="n">
-        <v>0.04569073766469955</v>
+        <v>0.009062875993549824</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>296</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1679.12</v>
+        <v>234</v>
       </c>
       <c r="C72" t="n">
-        <v>0.009993529878556728</v>
+        <v>0.0091772535815835</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>620.86</v>
+        <v>120</v>
       </c>
       <c r="C73" t="n">
-        <v>0.03051358461380005</v>
+        <v>0.01883599534630775</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>301</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>70</v>
+        <v>432.23</v>
       </c>
       <c r="C74" t="n">
-        <v>0.009818256832659245</v>
+        <v>0.009865438565611839</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>466</v>
+        <v>20</v>
       </c>
       <c r="C75" t="n">
-        <v>0.03799816966056824</v>
+        <v>0.02951739355921745</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>318</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>21.47</v>
+        <v>124</v>
       </c>
       <c r="C76" t="n">
-        <v>0.02466404251754284</v>
+        <v>0.01214286964386702</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>320</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>669.08</v>
+        <v>53</v>
       </c>
       <c r="C77" t="n">
-        <v>0.02171062491834164</v>
+        <v>0.02015063539147377</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>321</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>215.642</v>
+        <v>154.21</v>
       </c>
       <c r="C78" t="n">
-        <v>0.008395062759518623</v>
+        <v>0.01020512077957392</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>322</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>587.45</v>
+        <v>130</v>
       </c>
       <c r="C79" t="n">
-        <v>0.02070333622395992</v>
+        <v>0.01914274506270885</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>324</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>227.86</v>
+        <v>85</v>
       </c>
       <c r="C80" t="n">
-        <v>0.008597900159657001</v>
+        <v>0.01001131627708673</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>330</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>19.4</v>
+        <v>80</v>
       </c>
       <c r="C81" t="n">
-        <v>0.01726559177041054</v>
+        <v>0.009885368868708611</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>335</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>136</v>
+        <v>15</v>
       </c>
       <c r="C82" t="n">
-        <v>0.04379389062523842</v>
+        <v>0.009690449573099613</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>337</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>80</v>
+        <v>462</v>
       </c>
       <c r="C83" t="n">
-        <v>0.008644608780741692</v>
+        <v>0.03148467093706131</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>338</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>25</v>
+        <v>109.75</v>
       </c>
       <c r="C84" t="n">
-        <v>0.01477082073688507</v>
+        <v>0.0287589468061924</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>340</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>16</v>
+        <v>130</v>
       </c>
       <c r="C85" t="n">
-        <v>0.004917342215776443</v>
+        <v>0.02899111248552799</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>345</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>21.6</v>
+        <v>363</v>
       </c>
       <c r="C86" t="n">
-        <v>0.05649081617593765</v>
+        <v>0.02856843173503876</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>346</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>25</v>
+        <v>199</v>
       </c>
       <c r="C87" t="n">
-        <v>0.005118440836668015</v>
+        <v>0.02914593182504177</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>347</t>
         </is>
       </c>
       <c r="B88" t="n">
         <v>25</v>
       </c>
       <c r="C88" t="n">
-        <v>0.00728403776884079</v>
+        <v>0.03015174530446529</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>349</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>50</v>
+        <v>234</v>
       </c>
       <c r="C89" t="n">
-        <v>17.38616943359375</v>
+        <v>0.02953275665640831</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>350</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>200</v>
+        <v>35.31</v>
       </c>
       <c r="C90" t="n">
-        <v>0.07752801477909088</v>
+        <v>0.008054807782173157</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>353</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>9.59</v>
+        <v>11</v>
       </c>
       <c r="C91" t="n">
-        <v>0.02608267404139042</v>
+        <v>0.008427680470049381</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>361</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>50</v>
+        <v>225.5</v>
       </c>
       <c r="C92" t="n">
-        <v>0.01730941236019135</v>
+        <v>0.008496131747961044</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>376</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="C93" t="n">
-        <v>0.01547877676784992</v>
+        <v>0.008640622720122337</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>379</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>189.001</v>
+        <v>429.186</v>
       </c>
       <c r="C94" t="n">
-        <v>0.05203807353973389</v>
+        <v>0.008404577150940895</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>381</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>140</v>
+        <v>982.842</v>
       </c>
       <c r="C95" t="n">
-        <v>0.04525378718972206</v>
+        <v>0.008852655068039894</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>382</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>25</v>
+        <v>600.8</v>
       </c>
       <c r="C96" t="n">
-        <v>35.41880035400391</v>
+        <v>0.00850843358784914</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>383</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>130</v>
+        <v>40</v>
       </c>
       <c r="C97" t="n">
-        <v>0.04034808278083801</v>
+        <v>0.008550884202122688</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>388</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>102.91</v>
+        <v>60</v>
       </c>
       <c r="C98" t="n">
-        <v>7.842975616455078</v>
+        <v>0.008547211997210979</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>390</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="C99" t="n">
-        <v>0.002781974617391825</v>
+        <v>0.00849643349647522</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>393</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>737</v>
+        <v>523</v>
       </c>
       <c r="C100" t="n">
-        <v>0.03686110302805901</v>
+        <v>0.009024124592542648</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>394</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="C101" t="n">
-        <v>0.002803689101710916</v>
+        <v>0.0101155424490571</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>396</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>248</v>
+        <v>58</v>
       </c>
       <c r="C102" t="n">
-        <v>0.01301352120935917</v>
+        <v>0.01021558605134487</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>397</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>118</v>
+        <v>397.24</v>
       </c>
       <c r="C103" t="n">
-        <v>0.002798837143927813</v>
+        <v>0.01027453038841486</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>405</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>120</v>
+        <v>829.4400000000001</v>
       </c>
       <c r="C104" t="n">
-        <v>0.01875480450689793</v>
+        <v>0.009640630334615707</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>20</v>
+        <v>22.33</v>
       </c>
       <c r="C105" t="n">
-        <v>0.00790281780064106</v>
+        <v>0.01351733040064573</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>410</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>313.78</v>
+        <v>150</v>
       </c>
       <c r="C106" t="n">
-        <v>0.007385570555925369</v>
+        <v>0.009379510767757893</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>427</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="C107" t="n">
-        <v>0.008332712575793266</v>
+        <v>0.009428750723600388</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>428</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>23</v>
+        <v>378</v>
       </c>
       <c r="C108" t="n">
-        <v>0.06489843875169754</v>
+        <v>0.01008482743054628</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>429</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="C109" t="n">
-        <v>0.009998539462685585</v>
+        <v>0.0100189009681344</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>430</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="C110" t="n">
-        <v>0.03688632696866989</v>
+        <v>0.01061560399830341</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>432</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>96</v>
+        <v>233</v>
       </c>
       <c r="C111" t="n">
-        <v>0.02650344744324684</v>
+        <v>0.01100244838744402</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>434</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>173</v>
+        <v>250</v>
       </c>
       <c r="C112" t="n">
-        <v>0.02764728665351868</v>
+        <v>0.01697118207812309</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>436</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>200</v>
+        <v>185.761</v>
       </c>
       <c r="C113" t="n">
-        <v>0.02021162956953049</v>
+        <v>0.0028525919187814</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>439</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>22</v>
+        <v>283</v>
       </c>
       <c r="C114" t="n">
-        <v>92.58571624755859</v>
+        <v>0.01252945698797703</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>441</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="C115" t="n">
-        <v>0.009100177325308323</v>
+        <v>0.03030530549585819</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="C116" t="n">
-        <v>73.42344665527344</v>
+        <v>0.01216867938637733</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>450</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>40</v>
+        <v>93.2</v>
       </c>
       <c r="C117" t="n">
-        <v>34.36970901489258</v>
+        <v>0.01067317463457584</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>451</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>148.63</v>
+        <v>1054</v>
       </c>
       <c r="C118" t="n">
-        <v>0.002948870183899999</v>
+        <v>0.01306590624153614</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>453</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>25</v>
+        <v>1012.15</v>
       </c>
       <c r="C119" t="n">
-        <v>0.03681238368153572</v>
+        <v>0.009543139487504959</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>455</t>
         </is>
       </c>
       <c r="B120" t="n">
         <v>20</v>
       </c>
       <c r="C120" t="n">
-        <v>0.00298582692630589</v>
+        <v>332.3169250488281</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>463</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>103</v>
+        <v>21.5</v>
       </c>
       <c r="C121" t="n">
-        <v>0.03154756501317024</v>
+        <v>288.5719909667969</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>467</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>20</v>
+        <v>634.201</v>
       </c>
       <c r="C122" t="n">
-        <v>11.58847999572754</v>
+        <v>217.6519775390625</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>468</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>412.91</v>
+        <v>40</v>
       </c>
       <c r="C123" t="n">
-        <v>26.66502952575684</v>
+        <v>254.2578582763672</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>471</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>110</v>
+        <v>273</v>
       </c>
       <c r="C124" t="n">
-        <v>0.05189905688166618</v>
+        <v>320.2111206054688</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>475</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>193</v>
+        <v>297.5</v>
       </c>
       <c r="C125" t="n">
-        <v>17.64351272583008</v>
+        <v>288.9432067871094</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>476</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>140</v>
+        <v>88</v>
       </c>
       <c r="C126" t="n">
-        <v>0.05200537294149399</v>
+        <v>396.3298950195312</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>478</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>48</v>
+        <v>656.905</v>
       </c>
       <c r="C127" t="n">
-        <v>0.005410970654338598</v>
+        <v>753.4450073242188</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>486</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>80</v>
+        <v>68.89</v>
       </c>
       <c r="C128" t="n">
-        <v>0.05112966895103455</v>
+        <v>659.0205688476562</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>492</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>244.9</v>
+        <v>429.01</v>
       </c>
       <c r="C129" t="n">
-        <v>0.01856404170393944</v>
+        <v>370.3759155273438</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>497</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="C130" t="n">
-        <v>0.05853736400604248</v>
+        <v>301.5348205566406</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>507</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>63.1</v>
+        <v>156</v>
       </c>
       <c r="C131" t="n">
-        <v>0.004003870766609907</v>
+        <v>263.3158264160156</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>509</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>22.3</v>
+        <v>310</v>
       </c>
       <c r="C132" t="n">
-        <v>0.01478158496320248</v>
+        <v>297.7210998535156</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>54</v>
+        <v>37.8</v>
       </c>
       <c r="C133" t="n">
-        <v>0.06940440833568573</v>
+        <v>0.04522521048784256</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>510</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>108.817</v>
+        <v>103</v>
       </c>
       <c r="C134" t="n">
-        <v>0.006546401884406805</v>
+        <v>197.9739532470703</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>511</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>20</v>
+        <v>106.5</v>
       </c>
       <c r="C135" t="n">
-        <v>0.1539984345436096</v>
+        <v>0.02330818958580494</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>52</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>521.45</v>
+        <v>392.2</v>
       </c>
       <c r="C136" t="n">
-        <v>0.03158313035964966</v>
+        <v>0.039619080722332</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>521</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>492</v>
+        <v>95</v>
       </c>
       <c r="C137" t="n">
-        <v>0.007744364440441132</v>
+        <v>0.0163918249309063</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>524</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>379.75</v>
+        <v>1717.65</v>
       </c>
       <c r="C138" t="n">
-        <v>0.00931958295404911</v>
+        <v>0.02672472223639488</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>526</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>155</v>
+        <v>479.001</v>
       </c>
       <c r="C139" t="n">
-        <v>0.01013663411140442</v>
+        <v>0.105147048830986</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>53</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>50</v>
+        <v>163.23</v>
       </c>
       <c r="C140" t="n">
-        <v>0.01000302284955978</v>
+        <v>0.04246177151799202</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>533</t>
         </is>
       </c>
       <c r="B141" t="n">
         <v>20</v>
       </c>
       <c r="C141" t="n">
-        <v>0.01044150348752737</v>
+        <v>0.008886447176337242</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>536</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>20.5</v>
+        <v>706.26</v>
       </c>
       <c r="C142" t="n">
-        <v>0.01196535397320986</v>
+        <v>0.008532898500561714</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>537</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>647.01</v>
+        <v>20</v>
       </c>
       <c r="C143" t="n">
-        <v>0.03160326182842255</v>
+        <v>0.01294719148427248</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>539</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>252</v>
+        <v>512.48</v>
       </c>
       <c r="C144" t="n">
-        <v>0.009898279793560505</v>
+        <v>0.01422135066241026</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>541</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>53</v>
+        <v>250</v>
       </c>
       <c r="C145" t="n">
-        <v>0.01775013096630573</v>
+        <v>0.01374565251171589</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>543</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>25</v>
+        <v>604.45</v>
       </c>
       <c r="C146" t="n">
-        <v>0.004126487765461206</v>
+        <v>0.02760064229369164</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>546</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>551.876</v>
+        <v>10</v>
       </c>
       <c r="C147" t="n">
-        <v>0.006526901386678219</v>
+        <v>0.0150604946538806</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>553</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>498.52</v>
+        <v>671.546</v>
       </c>
       <c r="C148" t="n">
-        <v>0.01507227588444948</v>
+        <v>0.01581637933850288</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>556</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="C149" t="n">
-        <v>0.007621171418577433</v>
+        <v>0.01586790010333061</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>563</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="C150" t="n">
-        <v>0.007771969772875309</v>
+        <v>0.01590915769338608</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>571</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="C151" t="n">
-        <v>0.007904017344117165</v>
+        <v>0.02407786995172501</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>572</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>448.31</v>
+        <v>500</v>
       </c>
       <c r="C152" t="n">
-        <v>0.05538062006235123</v>
+        <v>0.02381515875458717</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>585</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>283.69</v>
+        <v>258</v>
       </c>
       <c r="C153" t="n">
-        <v>0.01196511741727591</v>
+        <v>0.0281461626291275</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>406</t>
+          <t>592</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>25</v>
+        <v>72.68300000000001</v>
       </c>
       <c r="C154" t="n">
-        <v>215.532958984375</v>
+        <v>0.03345175832509995</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>593</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>50</v>
+        <v>408.37</v>
       </c>
       <c r="C155" t="n">
-        <v>0.07599534094333649</v>
+        <v>0.03687918931245804</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>594</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>183</v>
+        <v>236</v>
       </c>
       <c r="C156" t="n">
-        <v>0.07264771312475204</v>
+        <v>0.03111372888088226</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>596</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>289</v>
+        <v>80</v>
       </c>
       <c r="C157" t="n">
-        <v>0.2271487712860107</v>
+        <v>0.03831331804394722</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>600</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>45</v>
+        <v>250</v>
       </c>
       <c r="C158" t="n">
-        <v>494.4349060058594</v>
+        <v>0.06616945564746857</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>601</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>23.9</v>
+        <v>150</v>
       </c>
       <c r="C159" t="n">
-        <v>0.1014536395668983</v>
+        <v>0.03982073813676834</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>602</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>280.22</v>
+        <v>134</v>
       </c>
       <c r="C160" t="n">
-        <v>0.113397441804409</v>
+        <v>0.02879053354263306</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>606</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="C161" t="n">
-        <v>204.828857421875</v>
+        <v>0.03277181833982468</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>608</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>148</v>
+        <v>40</v>
       </c>
       <c r="C162" t="n">
-        <v>0.02341342344880104</v>
+        <v>0.03026779554784298</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>614</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>163</v>
+        <v>491.93</v>
       </c>
       <c r="C163" t="n">
-        <v>0.03666191920638084</v>
+        <v>0.02634670957922935</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>616</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>23</v>
+        <v>160</v>
       </c>
       <c r="C164" t="n">
-        <v>0.0216717291623354</v>
+        <v>0.03412751108407974</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>617</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>23</v>
+        <v>320</v>
       </c>
       <c r="C165" t="n">
-        <v>0.009981674142181873</v>
+        <v>0.02108335308730602</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>618</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>142.4</v>
+        <v>208</v>
       </c>
       <c r="C166" t="n">
-        <v>0.006635059602558613</v>
+        <v>0.0188047531992197</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>619</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>66.97999999999999</v>
+        <v>180</v>
       </c>
       <c r="C167" t="n">
-        <v>0.01640553399920464</v>
+        <v>0.02571015991270542</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>620</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>641.0599999999999</v>
+        <v>410</v>
       </c>
       <c r="C168" t="n">
-        <v>0.007840042002499104</v>
+        <v>0.01231384743005037</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>623</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>1112.52</v>
+        <v>126.33</v>
       </c>
       <c r="C169" t="n">
-        <v>0.009447921998798847</v>
+        <v>0.02199527807533741</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>634</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>883</v>
+        <v>6</v>
       </c>
       <c r="C170" t="n">
-        <v>0.01147704012691975</v>
+        <v>0.02343471720814705</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>637</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>137.7</v>
+        <v>1193.425</v>
       </c>
       <c r="C171" t="n">
-        <v>0.02022950537502766</v>
+        <v>0.0220467746257782</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>454</t>
+          <t>639</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="C172" t="n">
-        <v>0.003693701699376106</v>
+        <v>0.012781897559762</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>454</t>
+          <t>640</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>7.8</v>
+        <v>104</v>
       </c>
       <c r="C173" t="n">
-        <v>0.007156681269407272</v>
+        <v>0.01908082515001297</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>650</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>20.76</v>
+        <v>919.24</v>
       </c>
       <c r="C174" t="n">
-        <v>0.04672554135322571</v>
+        <v>0.008174094371497631</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>463</t>
+          <t>656</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>147</v>
+        <v>1179.5</v>
       </c>
       <c r="C175" t="n">
-        <v>0.01069619599729776</v>
+        <v>0.007432799786329269</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>463</t>
+          <t>66</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>715.87</v>
+        <v>23</v>
       </c>
       <c r="C176" t="n">
-        <v>0.007160366512835026</v>
+        <v>0.03719865530729294</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>661</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>560.72</v>
+        <v>90</v>
       </c>
       <c r="C177" t="n">
-        <v>0.01681548357009888</v>
+        <v>0.007338891737163067</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>67</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>357.93</v>
+        <v>60</v>
       </c>
       <c r="C178" t="n">
-        <v>0.04652484506368637</v>
+        <v>0.03662710636854172</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>670</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>43</v>
+        <v>1496.51</v>
       </c>
       <c r="C179" t="n">
-        <v>0.008374114520847797</v>
+        <v>0.007912235334515572</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>685</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>120</v>
+        <v>161.53</v>
       </c>
       <c r="C180" t="n">
-        <v>0.012647470459342</v>
+        <v>0.008249806240200996</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>690</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="C181" t="n">
-        <v>0.04012102633714676</v>
+        <v>0.03268741816282272</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>476</t>
+          <t>691</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="C182" t="n">
-        <v>0.03705304116010666</v>
+        <v>0.03113386034965515</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>477</t>
+          <t>692</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>54</v>
+        <v>10.37</v>
       </c>
       <c r="C183" t="n">
-        <v>0.008485555648803711</v>
+        <v>0.03060888685286045</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>699</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>1062.081</v>
+        <v>228.36</v>
       </c>
       <c r="C184" t="n">
-        <v>0.0137778278440237</v>
+        <v>0.02523007430136204</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>70</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>549.77</v>
+        <v>60</v>
       </c>
       <c r="C185" t="n">
-        <v>0.008804040029644966</v>
+        <v>0.0356784500181675</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>709</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>50</v>
+        <v>135</v>
       </c>
       <c r="C186" t="n">
-        <v>0.01859965175390244</v>
+        <v>0.03154677897691727</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>71</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>976.28</v>
+        <v>20</v>
       </c>
       <c r="C187" t="n">
-        <v>0.02885130979120731</v>
+        <v>0.03420698642730713</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>714</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>510.35</v>
+        <v>55</v>
       </c>
       <c r="C188" t="n">
-        <v>0.00910363532602787</v>
+        <v>0.03284424170851707</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>717</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>100</v>
+        <v>409.86</v>
       </c>
       <c r="C189" t="n">
-        <v>0.02451282925903797</v>
+        <v>0.02630774304270744</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>722</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>20</v>
+        <v>174.38</v>
       </c>
       <c r="C190" t="n">
-        <v>0.02532501146197319</v>
+        <v>0.007832169532775879</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>731</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>45</v>
+        <v>260</v>
       </c>
       <c r="C191" t="n">
-        <v>0.01167202740907669</v>
+        <v>0.008397730067372322</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>739</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>65</v>
+        <v>204</v>
       </c>
       <c r="C192" t="n">
-        <v>0.0145203797146678</v>
+        <v>0.009033584967255592</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>754</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>50</v>
+        <v>103.96</v>
       </c>
       <c r="C193" t="n">
-        <v>0.01241828687489033</v>
+        <v>0.00873804185539484</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>77</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>22.69</v>
+        <v>40</v>
       </c>
       <c r="C194" t="n">
-        <v>0.02165278792381287</v>
+        <v>0.006824180483818054</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>775</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>220</v>
+        <v>5</v>
       </c>
       <c r="C195" t="n">
-        <v>0.009797139093279839</v>
+        <v>0.009311859495937824</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>780</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>45.88</v>
+        <v>677.575</v>
       </c>
       <c r="C196" t="n">
-        <v>0.042537622153759</v>
+        <v>0.009840285405516624</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>796</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>110</v>
+        <v>600.63</v>
       </c>
       <c r="C197" t="n">
-        <v>0.003958513028919697</v>
+        <v>0.009604679420590401</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>799</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="C198" t="n">
-        <v>0.01752414740622044</v>
+        <v>0.02351578511297703</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>806</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>18</v>
+        <v>200</v>
       </c>
       <c r="C199" t="n">
-        <v>0.01341744977980852</v>
+        <v>0.02329394780099392</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>2101.486</v>
+        <v>250</v>
       </c>
       <c r="C200" t="n">
-        <v>0.01049916166812181</v>
+        <v>0.007490519434213638</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>812</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>1573.5</v>
+        <v>506</v>
       </c>
       <c r="C201" t="n">
-        <v>0.006859143264591694</v>
+        <v>0.02376009151339531</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>814</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>702.21</v>
+        <v>23</v>
       </c>
       <c r="C202" t="n">
-        <v>0.009777411818504333</v>
+        <v>0.02163549140095711</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>826</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>275.79</v>
+        <v>1075.22</v>
       </c>
       <c r="C203" t="n">
-        <v>0.01258148066699505</v>
+        <v>0.0197935551404953</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>84</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>20</v>
+        <v>70.61</v>
       </c>
       <c r="C204" t="n">
-        <v>0.01746209897100925</v>
+        <v>0.009639378637075424</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>840</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="C205" t="n">
-        <v>0.01200625859200954</v>
+        <v>0.02092226594686508</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>847</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>180</v>
+        <v>1298.18</v>
       </c>
       <c r="C206" t="n">
-        <v>0.01274124719202518</v>
+        <v>0.02273069694638252</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>859</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>2</v>
+        <v>150</v>
       </c>
       <c r="C207" t="n">
-        <v>0.03894144296646118</v>
+        <v>0.008945229463279247</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>87</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C208" t="n">
-        <v>0.04766738414764404</v>
+        <v>0.0169554091989994</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>89</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>625</v>
+        <v>600</v>
       </c>
       <c r="C209" t="n">
-        <v>0.00682441983371973</v>
+        <v>0.02470176853239536</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>893</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>546</v>
+        <v>46</v>
       </c>
       <c r="C210" t="n">
-        <v>0.009182490408420563</v>
+        <v>0.009013181552290916</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>91</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>226</v>
+        <v>20</v>
       </c>
       <c r="C211" t="n">
-        <v>0.08142345398664474</v>
+        <v>0.01345964707434177</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>539</t>
+          <t>934</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>72.65000000000001</v>
+        <v>23</v>
       </c>
       <c r="C212" t="n">
-        <v>0.009554260410368443</v>
+        <v>0.009166350588202477</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>539</t>
+          <t>937</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>122.42</v>
+        <v>115</v>
       </c>
       <c r="C213" t="n">
-        <v>0.05710584670305252</v>
+        <v>0.009701003320515156</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>543</t>
+          <t>941</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>811.87</v>
+        <v>150.174</v>
       </c>
       <c r="C214" t="n">
-        <v>0.01381468214094639</v>
+        <v>0.01074584387242794</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>543</t>
+          <t>95</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>464.1</v>
+        <v>13.785</v>
       </c>
       <c r="C215" t="n">
-        <v>0.06223514676094055</v>
+        <v>0.01270201615989208</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>957</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>20</v>
+        <v>86.47</v>
       </c>
       <c r="C216" t="n">
-        <v>0.008041969500482082</v>
+        <v>0.01085235923528671</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>969</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>75</v>
+        <v>366.7</v>
       </c>
       <c r="C217" t="n">
-        <v>0.01105100568383932</v>
+        <v>0.01103248819708824</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>97</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>50</v>
+        <v>175.97</v>
       </c>
       <c r="C218" t="n">
-        <v>0.003288944019004703</v>
+        <v>0.01095821242779493</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>98</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>840.53</v>
+        <v>2202.53</v>
       </c>
       <c r="C219" t="n">
-        <v>0.0233540590852499</v>
+        <v>0.01218636799603701</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>984</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>730.89</v>
+        <v>209.19</v>
       </c>
       <c r="C220" t="n">
-        <v>0.01282608974725008</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>554</t>
-        </is>
-      </c>
-      <c r="B221" t="n">
-        <v>46</v>
-      </c>
-      <c r="C221" t="n">
-        <v>0.01068741362541914</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>555</t>
-        </is>
-      </c>
-      <c r="B222" t="n">
-        <v>100</v>
-      </c>
-      <c r="C222" t="n">
-        <v>0.009548602625727654</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>560</t>
-        </is>
-      </c>
-      <c r="B223" t="n">
-        <v>317.72</v>
-      </c>
-      <c r="C223" t="n">
-        <v>0.01028729230165482</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>580</t>
-        </is>
-      </c>
-      <c r="B224" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="C224" t="n">
-        <v>0.01559178531169891</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>585</t>
-        </is>
-      </c>
-      <c r="B225" t="n">
-        <v>191.16</v>
-      </c>
-      <c r="C225" t="n">
-        <v>0.01729856617748737</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>586</t>
-        </is>
-      </c>
-      <c r="B226" t="n">
-        <v>30</v>
-      </c>
-      <c r="C226" t="n">
-        <v>0.01260233856737614</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>593</t>
-        </is>
-      </c>
-      <c r="B227" t="n">
-        <v>570</v>
-      </c>
-      <c r="C227" t="n">
-        <v>0.01510519348084927</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>593</t>
-        </is>
-      </c>
-      <c r="B228" t="n">
-        <v>374</v>
-      </c>
-      <c r="C228" t="n">
-        <v>0.005202497355639935</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>594</t>
-        </is>
-      </c>
-      <c r="B229" t="n">
-        <v>134.5</v>
-      </c>
-      <c r="C229" t="n">
-        <v>0.01498414296656847</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="B230" t="n">
-        <v>200</v>
-      </c>
-      <c r="C230" t="n">
-        <v>0.0179650355130434</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="B231" t="n">
-        <v>100</v>
-      </c>
-      <c r="C231" t="n">
-        <v>0.04486089572310448</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>601</t>
-        </is>
-      </c>
-      <c r="B232" t="n">
-        <v>108</v>
-      </c>
-      <c r="C232" t="n">
-        <v>0.009222099557518959</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>602</t>
-        </is>
-      </c>
-      <c r="B233" t="n">
-        <v>50</v>
-      </c>
-      <c r="C233" t="n">
-        <v>0.05095777660608292</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>606</t>
-        </is>
-      </c>
-      <c r="B234" t="n">
-        <v>50</v>
-      </c>
-      <c r="C234" t="n">
-        <v>0.04895521700382233</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>606</t>
-        </is>
-      </c>
-      <c r="B235" t="n">
-        <v>250</v>
-      </c>
-      <c r="C235" t="n">
-        <v>0.008517390117049217</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>614</t>
-        </is>
-      </c>
-      <c r="B236" t="n">
-        <v>600</v>
-      </c>
-      <c r="C236" t="n">
-        <v>0.04296534508466721</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>620</t>
-        </is>
-      </c>
-      <c r="B237" t="n">
-        <v>50</v>
-      </c>
-      <c r="C237" t="n">
-        <v>0.01245040167123079</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>620</t>
-        </is>
-      </c>
-      <c r="B238" t="n">
-        <v>60</v>
-      </c>
-      <c r="C238" t="n">
-        <v>312.7024536132812</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>628</t>
-        </is>
-      </c>
-      <c r="B239" t="n">
-        <v>150</v>
-      </c>
-      <c r="C239" t="n">
-        <v>329.1344604492188</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>630</t>
-        </is>
-      </c>
-      <c r="B240" t="n">
-        <v>300</v>
-      </c>
-      <c r="C240" t="n">
-        <v>233.7984619140625</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>634</t>
-        </is>
-      </c>
-      <c r="B241" t="n">
-        <v>6</v>
-      </c>
-      <c r="C241" t="n">
-        <v>0.0152726648375392</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>634</t>
-        </is>
-      </c>
-      <c r="B242" t="n">
-        <v>30</v>
-      </c>
-      <c r="C242" t="n">
-        <v>0.2776125371456146</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>637</t>
-        </is>
-      </c>
-      <c r="B243" t="n">
-        <v>967.6900000000001</v>
-      </c>
-      <c r="C243" t="n">
-        <v>0.02189731784164906</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>637</t>
-        </is>
-      </c>
-      <c r="B244" t="n">
-        <v>222.51</v>
-      </c>
-      <c r="C244" t="n">
-        <v>0.1305689513683319</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
-      <c r="B245" t="n">
-        <v>740.54</v>
-      </c>
-      <c r="C245" t="n">
-        <v>0.03121325373649597</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
-      <c r="B246" t="n">
-        <v>256.83</v>
-      </c>
-      <c r="C246" t="n">
-        <v>0.09261111170053482</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="B247" t="n">
-        <v>1279.13</v>
-      </c>
-      <c r="C247" t="n">
-        <v>0.00958568137139082</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="B248" t="n">
-        <v>762.72</v>
-      </c>
-      <c r="C248" t="n">
-        <v>0.007719970308244228</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>657</t>
-        </is>
-      </c>
-      <c r="B249" t="n">
-        <v>20</v>
-      </c>
-      <c r="C249" t="n">
-        <v>0.0332900695502758</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>659</t>
-        </is>
-      </c>
-      <c r="B250" t="n">
-        <v>125</v>
-      </c>
-      <c r="C250" t="n">
-        <v>23.64950942993164</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="B251" t="n">
-        <v>25</v>
-      </c>
-      <c r="C251" t="n">
-        <v>0.01536850444972515</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>670</t>
-        </is>
-      </c>
-      <c r="B252" t="n">
-        <v>1272.03</v>
-      </c>
-      <c r="C252" t="n">
-        <v>85.54519653320312</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>670</t>
-        </is>
-      </c>
-      <c r="B253" t="n">
-        <v>752</v>
-      </c>
-      <c r="C253" t="n">
-        <v>0.008379103615880013</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="B254" t="n">
-        <v>25</v>
-      </c>
-      <c r="C254" t="n">
-        <v>42.87767791748047</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>676</t>
-        </is>
-      </c>
-      <c r="B255" t="n">
-        <v>200</v>
-      </c>
-      <c r="C255" t="n">
-        <v>0.05650248005986214</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>682</t>
-        </is>
-      </c>
-      <c r="B256" t="n">
-        <v>30</v>
-      </c>
-      <c r="C256" t="n">
-        <v>0.0831293985247612</v>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="B257" t="n">
-        <v>150</v>
-      </c>
-      <c r="C257" t="n">
-        <v>0.02492029592394829</v>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="B258" t="n">
-        <v>100</v>
-      </c>
-      <c r="C258" t="n">
-        <v>0.009203514084219933</v>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="B259" t="n">
-        <v>100</v>
-      </c>
-      <c r="C259" t="n">
-        <v>0.01067865639925003</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>699</t>
-        </is>
-      </c>
-      <c r="B260" t="n">
-        <v>150</v>
-      </c>
-      <c r="C260" t="n">
-        <v>0.01391868852078915</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="B261" t="n">
-        <v>300</v>
-      </c>
-      <c r="C261" t="n">
-        <v>0.02176732942461967</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="B262" t="n">
-        <v>90</v>
-      </c>
-      <c r="C262" t="n">
-        <v>0.09643884003162384</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>714</t>
-        </is>
-      </c>
-      <c r="B263" t="n">
-        <v>83</v>
-      </c>
-      <c r="C263" t="n">
-        <v>0.005093944724649191</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>714</t>
-        </is>
-      </c>
-      <c r="B264" t="n">
-        <v>120</v>
-      </c>
-      <c r="C264" t="n">
-        <v>0.00412782421335578</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>715</t>
-        </is>
-      </c>
-      <c r="B265" t="n">
-        <v>100</v>
-      </c>
-      <c r="C265" t="n">
-        <v>0.02801265940070152</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>717</t>
-        </is>
-      </c>
-      <c r="B266" t="n">
-        <v>70</v>
-      </c>
-      <c r="C266" t="n">
-        <v>0.005765012931078672</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>722</t>
-        </is>
-      </c>
-      <c r="B267" t="n">
-        <v>158</v>
-      </c>
-      <c r="C267" t="n">
-        <v>0.01534339319914579</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>731</t>
-        </is>
-      </c>
-      <c r="B268" t="n">
-        <v>200</v>
-      </c>
-      <c r="C268" t="n">
-        <v>299.9405517578125</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>739</t>
-        </is>
-      </c>
-      <c r="B269" t="n">
-        <v>120</v>
-      </c>
-      <c r="C269" t="n">
-        <v>186.9662322998047</v>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>739</t>
-        </is>
-      </c>
-      <c r="B270" t="n">
-        <v>50</v>
-      </c>
-      <c r="C270" t="n">
-        <v>0.004232543520629406</v>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>742</t>
-        </is>
-      </c>
-      <c r="B271" t="n">
-        <v>150</v>
-      </c>
-      <c r="C271" t="n">
-        <v>197.6841430664062</v>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="B272" t="n">
-        <v>90</v>
-      </c>
-      <c r="C272" t="n">
-        <v>0.006465302314609289</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>775</t>
-        </is>
-      </c>
-      <c r="B273" t="n">
-        <v>20</v>
-      </c>
-      <c r="C273" t="n">
-        <v>14.41665077209473</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>775</t>
-        </is>
-      </c>
-      <c r="B274" t="n">
-        <v>20</v>
-      </c>
-      <c r="C274" t="n">
-        <v>0.004266423173248768</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="B275" t="n">
-        <v>50</v>
-      </c>
-      <c r="C275" t="n">
-        <v>0.05894159153103828</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
-      </c>
-      <c r="B276" t="n">
-        <v>563.8</v>
-      </c>
-      <c r="C276" t="n">
-        <v>39.46859741210938</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
-      </c>
-      <c r="B277" t="n">
-        <v>115</v>
-      </c>
-      <c r="C277" t="n">
-        <v>0.04392314329743385</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>783</t>
-        </is>
-      </c>
-      <c r="B278" t="n">
-        <v>165</v>
-      </c>
-      <c r="C278" t="n">
-        <v>11.36111640930176</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>799</t>
-        </is>
-      </c>
-      <c r="B279" t="n">
-        <v>10.62</v>
-      </c>
-      <c r="C279" t="n">
-        <v>0.0170659851282835</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>803</t>
-        </is>
-      </c>
-      <c r="B280" t="n">
-        <v>45.29</v>
-      </c>
-      <c r="C280" t="n">
-        <v>0.004813612438738346</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>812</t>
-        </is>
-      </c>
-      <c r="B281" t="n">
-        <v>501.57</v>
-      </c>
-      <c r="C281" t="n">
-        <v>0.004822300281375647</v>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>812</t>
-        </is>
-      </c>
-      <c r="B282" t="n">
-        <v>260</v>
-      </c>
-      <c r="C282" t="n">
-        <v>0.03808764740824699</v>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>826</t>
-        </is>
-      </c>
-      <c r="B283" t="n">
-        <v>1211.07</v>
-      </c>
-      <c r="C283" t="n">
-        <v>0.01286169420927763</v>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>826</t>
-        </is>
-      </c>
-      <c r="B284" t="n">
-        <v>574.424</v>
-      </c>
-      <c r="C284" t="n">
-        <v>0.03486040234565735</v>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>847</t>
-        </is>
-      </c>
-      <c r="B285" t="n">
-        <v>1479.06</v>
-      </c>
-      <c r="C285" t="n">
-        <v>0.01564832963049412</v>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>847</t>
-        </is>
-      </c>
-      <c r="B286" t="n">
-        <v>478.84</v>
-      </c>
-      <c r="C286" t="n">
-        <v>0.01329702418297529</v>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>851</t>
-        </is>
-      </c>
-      <c r="B287" t="n">
-        <v>50</v>
-      </c>
-      <c r="C287" t="n">
-        <v>0.01735389232635498</v>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>854</t>
-        </is>
-      </c>
-      <c r="B288" t="n">
-        <v>80</v>
-      </c>
-      <c r="C288" t="n">
-        <v>0.008278822526335716</v>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="B289" t="n">
-        <v>40</v>
-      </c>
-      <c r="C289" t="n">
-        <v>0.003975659608840942</v>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="B290" t="n">
-        <v>40</v>
-      </c>
-      <c r="C290" t="n">
-        <v>0.009267018176615238</v>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="B291" t="n">
-        <v>50</v>
-      </c>
-      <c r="C291" t="n">
-        <v>0.02365094795823097</v>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>891</t>
-        </is>
-      </c>
-      <c r="B292" t="n">
-        <v>150</v>
-      </c>
-      <c r="C292" t="n">
-        <v>0.009722099639475346</v>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>898</t>
-        </is>
-      </c>
-      <c r="B293" t="n">
-        <v>25</v>
-      </c>
-      <c r="C293" t="n">
-        <v>0.01492714323103428</v>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="B294" t="n">
-        <v>22.25</v>
-      </c>
-      <c r="C294" t="n">
-        <v>0.02071735076606274</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="B295" t="n">
-        <v>44.75</v>
-      </c>
-      <c r="C295" t="n">
-        <v>0.05674248188734055</v>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="B296" t="n">
-        <v>110</v>
-      </c>
-      <c r="C296" t="n">
-        <v>0.04772142693400383</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>937</t>
-        </is>
-      </c>
-      <c r="B297" t="n">
-        <v>2.674</v>
-      </c>
-      <c r="C297" t="n">
-        <v>0.0118465218693018</v>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>937</t>
-        </is>
-      </c>
-      <c r="B298" t="n">
-        <v>50</v>
-      </c>
-      <c r="C298" t="n">
-        <v>0.009878085926175117</v>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="B299" t="n">
-        <v>50</v>
-      </c>
-      <c r="C299" t="n">
-        <v>0.01790676452219486</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>941</t>
-        </is>
-      </c>
-      <c r="B300" t="n">
-        <v>314.75</v>
-      </c>
-      <c r="C300" t="n">
-        <v>0.1909618675708771</v>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>941</t>
-        </is>
-      </c>
-      <c r="B301" t="n">
-        <v>45</v>
-      </c>
-      <c r="C301" t="n">
-        <v>0.009910658933222294</v>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="B302" t="n">
-        <v>180</v>
-      </c>
-      <c r="C302" t="n">
-        <v>0.01706438884139061</v>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="B303" t="n">
-        <v>106</v>
-      </c>
-      <c r="C303" t="n">
-        <v>0.04638350754976273</v>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" t="inlineStr">
-        <is>
-          <t>957</t>
-        </is>
-      </c>
-      <c r="B304" t="n">
-        <v>207</v>
-      </c>
-      <c r="C304" t="n">
-        <v>0.06487013399600983</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="inlineStr">
-        <is>
-          <t>957</t>
-        </is>
-      </c>
-      <c r="B305" t="n">
-        <v>155</v>
-      </c>
-      <c r="C305" t="n">
-        <v>0.009635883383452892</v>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="inlineStr">
-        <is>
-          <t>969</t>
-        </is>
-      </c>
-      <c r="B306" t="n">
-        <v>1266</v>
-      </c>
-      <c r="C306" t="n">
-        <v>0.08032514899969101</v>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="inlineStr">
-        <is>
-          <t>969</t>
-        </is>
-      </c>
-      <c r="B307" t="n">
-        <v>105</v>
-      </c>
-      <c r="C307" t="n">
-        <v>0.006205456331372261</v>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="B308" t="n">
-        <v>240</v>
-      </c>
-      <c r="C308" t="n">
-        <v>0.009998789057135582</v>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="B309" t="n">
-        <v>1927.23</v>
-      </c>
-      <c r="C309" t="n">
-        <v>0.00998231116682291</v>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="B310" t="n">
-        <v>849.79</v>
-      </c>
-      <c r="C310" t="n">
-        <v>0.0451401062309742</v>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" t="inlineStr">
-        <is>
-          <t>984</t>
-        </is>
-      </c>
-      <c r="B311" t="n">
-        <v>832</v>
-      </c>
-      <c r="C311" t="n">
-        <v>0.02100706472992897</v>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" t="inlineStr">
-        <is>
-          <t>984</t>
-        </is>
-      </c>
-      <c r="B312" t="n">
-        <v>367</v>
-      </c>
-      <c r="C312" t="n">
-        <v>0.00641962606459856</v>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="inlineStr">
-        <is>
-          <t>989</t>
-        </is>
-      </c>
-      <c r="B313" t="n">
-        <v>20</v>
-      </c>
-      <c r="C313" t="n">
-        <v>0.01430755574256182</v>
+        <v>2060.73486328125</v>
       </c>
     </row>
   </sheetData>
